--- a/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="96">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -159,6 +159,12 @@
     <t>Generic Information</t>
   </si>
   <si>
+    <t>FOPH-021</t>
+  </si>
+  <si>
+    <t>Identical laboratory-test data are already stored in the FOPH database. The document is therefore considered a duplicate.</t>
+  </si>
+  <si>
     <t>warning</t>
   </si>
   <si>
@@ -186,85 +192,85 @@
     <t>The required anonymization for the reported organism was violated. The following field(s) are affected: %fields%</t>
   </si>
   <si>
+    <t>FOPH-022</t>
+  </si>
+  <si>
+    <t>Received multiple service requests without a basedOn attribute. Only the data contained in the service request referenced by the basedOn attribute in the DiagnosticReport are imported. If you want to specify an original orderer use the basedOn attribute on the primary service request to reference the secondary service request.</t>
+  </si>
+  <si>
+    <t>FOPH-023</t>
+  </si>
+  <si>
+    <t>Local patient identifier (MR type) is present, but patient name fields do not have dataAbsentReason. Names should not be transmitted when using local identifiers.</t>
+  </si>
+  <si>
+    <t>FOPH-011</t>
+  </si>
+  <si>
+    <t>The material is already specified by the leading code. The additional material specified in specimen.type will be ignored.</t>
+  </si>
+  <si>
+    <t>FOPH-010</t>
+  </si>
+  <si>
+    <t>Attention, the code %code% (%codeSystem%) expires on %validTo%. Please adjust your systems by this date.</t>
+  </si>
+  <si>
+    <t>FOPH-019</t>
+  </si>
+  <si>
+    <t>The combination of postal code &amp; city in the practitioner orderer address element could not be found in the FOPH location database.</t>
+  </si>
+  <si>
+    <t>FOPH-018</t>
+  </si>
+  <si>
+    <t>The combination of postal code &amp; city in the organization orderer address element could not be found in the FOPH location database.</t>
+  </si>
+  <si>
+    <t>FOPH-001</t>
+  </si>
+  <si>
+    <t>Generic Warning</t>
+  </si>
+  <si>
+    <t>FOPH-006</t>
+  </si>
+  <si>
+    <t>The following elements for the patient's address are expected: %missingElements%.</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>If the rule is violated, the resource is not conformant.</t>
+  </si>
+  <si>
+    <t>FOPH-009</t>
+  </si>
+  <si>
+    <t>The transmitted code %code% (%codeSystem%) is outside the defined validity period %validFrom% - %validTo%.</t>
+  </si>
+  <si>
+    <t>FOPH-016</t>
+  </si>
+  <si>
+    <t>The country code specified under patient address could not resolved. An ISO 3166 2 or 3 letter code is expected.</t>
+  </si>
+  <si>
+    <t>FOPH-002</t>
+  </si>
+  <si>
+    <t>Generic Error</t>
+  </si>
+  <si>
     <t>FOPH-020</t>
   </si>
   <si>
-    <t>The effectiveDateTime-element indicates that the test was executed more than %testExecutionDateRejectionThresholdInDays% days ago. Assuming that this test has already been reported, the document is considered a duplicate. Duplicates are accepted on ABN/Test but not on the productive environment.</t>
-  </si>
-  <si>
-    <t>FOPH-022</t>
-  </si>
-  <si>
-    <t>Received multiple service requests without a basedOn attribute. Only the data contained in the service request referenced by the basedOn attribute in the DiagnosticReport are imported. If you want to specify an original orderer use the basedOn attribute on the primary service request to reference the secondary service request.</t>
-  </si>
-  <si>
-    <t>FOPH-011</t>
-  </si>
-  <si>
-    <t>The material is already specified by the leading code. The additional material specified in specimen.type will be ignored.</t>
-  </si>
-  <si>
-    <t>FOPH-010</t>
-  </si>
-  <si>
-    <t>Attention, the code %code% (%codeSystem%) expires on %validTo%. Please adjust your systems by this date.</t>
-  </si>
-  <si>
-    <t>FOPH-019</t>
-  </si>
-  <si>
-    <t>The combination of postal code &amp; city in the practitioner orderer address element could not be found in the FOPH location database.</t>
-  </si>
-  <si>
-    <t>FOPH-018</t>
-  </si>
-  <si>
-    <t>The combination of postal code &amp; city in the organization orderer address element could not be found in the FOPH location database.</t>
-  </si>
-  <si>
-    <t>FOPH-021</t>
-  </si>
-  <si>
-    <t>Identical laboratory-test data are already stored in the FOPH database. The document is therefore considered a duplicate. Duplicates are accepted on ABN/Test but not on the productive environment.</t>
-  </si>
-  <si>
-    <t>FOPH-001</t>
-  </si>
-  <si>
-    <t>Generic Warning</t>
-  </si>
-  <si>
-    <t>FOPH-006</t>
-  </si>
-  <si>
-    <t>The following elements for the patient's address are expected: %missingElements%.</t>
-  </si>
-  <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t>If the rule is violated, the resource is not conformant.</t>
-  </si>
-  <si>
-    <t>FOPH-009</t>
-  </si>
-  <si>
-    <t>The transmitted code %code% (%codeSystem%) is outside the defined validity period %validFrom% - %validTo%.</t>
-  </si>
-  <si>
-    <t>FOPH-016</t>
-  </si>
-  <si>
-    <t>The country code specified under patient address could not resolved. An ISO 3166 2 or 3 letter code is expected.</t>
-  </si>
-  <si>
-    <t>FOPH-002</t>
-  </si>
-  <si>
-    <t>Generic Error</t>
+    <t>The effectiveDateTime-element indicates that the test was executed more than %testExecutionDateRejectionThresholdInDays% days ago. Assuming that this test has already been reported, the document is considered a duplicate. Please contact FOPH if you believe that this document must still be processed.</t>
   </si>
   <si>
     <t>FOPH-007</t>
@@ -606,7 +612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -651,7 +657,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>48</v>
@@ -659,21 +665,21 @@
       <c r="C4" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>50</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="D5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -916,6 +922,18 @@
         <v>93</v>
       </c>
       <c r="D25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D26" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
+++ b/ig/ch-elm/CodeSystem-ch-elm-foph-business-rules.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
